--- a/resources/templates/standard/M2100-01.xlsx
+++ b/resources/templates/standard/M2100-01.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>LOT 관리 기준서</t>
   </si>
@@ -661,12 +664,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -701,21 +706,21 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -825,7 +830,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -843,7 +848,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
@@ -861,13 +866,13 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
       <c r="AG4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH4" s="8"/>
       <c r="AI4" s="8"/>
       <c r="AJ4" s="8"/>
       <c r="AK4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL4" s="7"/>
       <c r="AM4" s="7"/>
@@ -1547,25 +1552,25 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="21"/>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
       <c r="H18" s="21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="21"/>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N18" s="21"/>
       <c r="O18" s="21"/>
@@ -1597,7 +1602,7 @@
       <c r="AO18" s="21"/>
       <c r="AP18" s="21"/>
       <c r="AQ18" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR18" s="21"/>
       <c r="AS18" s="21"/>
